--- a/outputs/tables/mst_selected_stocks_all_methods_with_costs_taxes.xlsx
+++ b/outputs/tables/mst_selected_stocks_all_methods_with_costs_taxes.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,62 +421,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>degree</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>degree_centrality</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>betweenness</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>closeness</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rebalance_date</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>yahoo_ticker</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>sector</t>
         </is>
@@ -510,7 +498,7 @@
         <v>0.4380952380952381</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4021728235821736</v>
+        <v>0.4021728235821735</v>
       </c>
       <c r="F2" t="n">
         <v>2018</v>
@@ -518,7 +506,7 @@
       <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I2" t="inlineStr">
@@ -566,7 +554,7 @@
       <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I3" t="inlineStr">
@@ -614,7 +602,7 @@
       <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I4" t="inlineStr">
@@ -662,7 +650,7 @@
       <c r="G5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I5" t="inlineStr">
@@ -710,7 +698,7 @@
       <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I6" t="inlineStr">
@@ -758,7 +746,7 @@
       <c r="G7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I7" t="inlineStr">
@@ -798,7 +786,7 @@
         <v>0.2079365079365079</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3589760153607273</v>
+        <v>0.3589760153607272</v>
       </c>
       <c r="F8" t="n">
         <v>2018</v>
@@ -806,7 +794,7 @@
       <c r="G8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I8" t="inlineStr">
@@ -854,7 +842,7 @@
       <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I9" t="inlineStr">
@@ -902,7 +890,7 @@
       <c r="G10" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I10" t="inlineStr">
@@ -942,7 +930,7 @@
         <v>0.1095238095238095</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3439965429296708</v>
+        <v>0.3439965429296707</v>
       </c>
       <c r="F11" t="n">
         <v>2018</v>
@@ -950,7 +938,7 @@
       <c r="G11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="H11" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I11" t="inlineStr">
@@ -998,7 +986,7 @@
       <c r="G12" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="H12" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I12" t="inlineStr">
@@ -1046,7 +1034,7 @@
       <c r="G13" t="n">
         <v>2</v>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="H13" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I13" t="inlineStr">
@@ -1094,7 +1082,7 @@
       <c r="G14" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="H14" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I14" t="inlineStr">
@@ -1142,7 +1130,7 @@
       <c r="G15" t="n">
         <v>2</v>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="H15" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I15" t="inlineStr">
@@ -1182,7 +1170,7 @@
         <v>0.3666666666666666</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2840861031715121</v>
+        <v>0.284086103171512</v>
       </c>
       <c r="F16" t="n">
         <v>2018</v>
@@ -1190,7 +1178,7 @@
       <c r="G16" t="n">
         <v>2</v>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="H16" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I16" t="inlineStr">
@@ -1238,7 +1226,7 @@
       <c r="G17" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="H17" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I17" t="inlineStr">
@@ -1286,7 +1274,7 @@
       <c r="G18" t="n">
         <v>2</v>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="H18" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I18" t="inlineStr">
@@ -1334,7 +1322,7 @@
       <c r="G19" t="n">
         <v>2</v>
       </c>
-      <c r="H19" s="2" t="n">
+      <c r="H19" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I19" t="inlineStr">
@@ -1382,7 +1370,7 @@
       <c r="G20" t="n">
         <v>2</v>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="H20" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I20" t="inlineStr">
@@ -1430,7 +1418,7 @@
       <c r="G21" t="n">
         <v>2</v>
       </c>
-      <c r="H21" s="2" t="n">
+      <c r="H21" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I21" t="inlineStr">
@@ -1478,7 +1466,7 @@
       <c r="G22" t="n">
         <v>3</v>
       </c>
-      <c r="H22" s="2" t="n">
+      <c r="H22" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I22" t="inlineStr">
@@ -1518,7 +1506,7 @@
         <v>0.307936507936508</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2404705896685249</v>
+        <v>0.240470589668525</v>
       </c>
       <c r="F23" t="n">
         <v>2018</v>
@@ -1526,7 +1514,7 @@
       <c r="G23" t="n">
         <v>3</v>
       </c>
-      <c r="H23" s="2" t="n">
+      <c r="H23" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I23" t="inlineStr">
@@ -1574,7 +1562,7 @@
       <c r="G24" t="n">
         <v>3</v>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="H24" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I24" t="inlineStr">
@@ -1622,7 +1610,7 @@
       <c r="G25" t="n">
         <v>3</v>
       </c>
-      <c r="H25" s="2" t="n">
+      <c r="H25" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I25" t="inlineStr">
@@ -1670,7 +1658,7 @@
       <c r="G26" t="n">
         <v>3</v>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="H26" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I26" t="inlineStr">
@@ -1718,7 +1706,7 @@
       <c r="G27" t="n">
         <v>3</v>
       </c>
-      <c r="H27" s="2" t="n">
+      <c r="H27" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I27" t="inlineStr">
@@ -1758,7 +1746,7 @@
         <v>0.1603174603174603</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1717270804386007</v>
+        <v>0.1717270804386008</v>
       </c>
       <c r="F28" t="n">
         <v>2018</v>
@@ -1766,7 +1754,7 @@
       <c r="G28" t="n">
         <v>3</v>
       </c>
-      <c r="H28" s="2" t="n">
+      <c r="H28" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I28" t="inlineStr">
@@ -1806,7 +1794,7 @@
         <v>0.246031746031746</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2395811782073702</v>
+        <v>0.2395811782073703</v>
       </c>
       <c r="F29" t="n">
         <v>2018</v>
@@ -1814,7 +1802,7 @@
       <c r="G29" t="n">
         <v>3</v>
       </c>
-      <c r="H29" s="2" t="n">
+      <c r="H29" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I29" t="inlineStr">
@@ -1862,7 +1850,7 @@
       <c r="G30" t="n">
         <v>3</v>
       </c>
-      <c r="H30" s="2" t="n">
+      <c r="H30" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I30" t="inlineStr">
@@ -1910,7 +1898,7 @@
       <c r="G31" t="n">
         <v>3</v>
       </c>
-      <c r="H31" s="2" t="n">
+      <c r="H31" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I31" t="inlineStr">
@@ -1958,7 +1946,7 @@
       <c r="G32" t="n">
         <v>4</v>
       </c>
-      <c r="H32" s="2" t="n">
+      <c r="H32" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I32" t="inlineStr">
@@ -1998,7 +1986,7 @@
         <v>0.6492063492063492</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3346713408710877</v>
+        <v>0.3346713408710879</v>
       </c>
       <c r="F33" t="n">
         <v>2018</v>
@@ -2006,7 +1994,7 @@
       <c r="G33" t="n">
         <v>4</v>
       </c>
-      <c r="H33" s="2" t="n">
+      <c r="H33" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I33" t="inlineStr">
@@ -2054,7 +2042,7 @@
       <c r="G34" t="n">
         <v>4</v>
       </c>
-      <c r="H34" s="2" t="n">
+      <c r="H34" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I34" t="inlineStr">
@@ -2094,7 +2082,7 @@
         <v>0.1619047619047619</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2170842854356669</v>
+        <v>0.2170842854356668</v>
       </c>
       <c r="F35" t="n">
         <v>2018</v>
@@ -2102,7 +2090,7 @@
       <c r="G35" t="n">
         <v>4</v>
       </c>
-      <c r="H35" s="2" t="n">
+      <c r="H35" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I35" t="inlineStr">
@@ -2142,7 +2130,7 @@
         <v>0.5666666666666667</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3445292773990736</v>
+        <v>0.3445292773990735</v>
       </c>
       <c r="F36" t="n">
         <v>2018</v>
@@ -2150,7 +2138,7 @@
       <c r="G36" t="n">
         <v>4</v>
       </c>
-      <c r="H36" s="2" t="n">
+      <c r="H36" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I36" t="inlineStr">
@@ -2190,7 +2178,7 @@
         <v>0.2523809523809524</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2671079256816084</v>
+        <v>0.2671079256816083</v>
       </c>
       <c r="F37" t="n">
         <v>2018</v>
@@ -2198,7 +2186,7 @@
       <c r="G37" t="n">
         <v>4</v>
       </c>
-      <c r="H37" s="2" t="n">
+      <c r="H37" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I37" t="inlineStr">
@@ -2246,7 +2234,7 @@
       <c r="G38" t="n">
         <v>4</v>
       </c>
-      <c r="H38" s="2" t="n">
+      <c r="H38" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I38" t="inlineStr">
@@ -2294,7 +2282,7 @@
       <c r="G39" t="n">
         <v>4</v>
       </c>
-      <c r="H39" s="2" t="n">
+      <c r="H39" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I39" t="inlineStr">
@@ -2334,7 +2322,7 @@
         <v>0.1095238095238095</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2004325586620658</v>
+        <v>0.2004325586620657</v>
       </c>
       <c r="F40" t="n">
         <v>2018</v>
@@ -2342,7 +2330,7 @@
       <c r="G40" t="n">
         <v>4</v>
       </c>
-      <c r="H40" s="2" t="n">
+      <c r="H40" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I40" t="inlineStr">
@@ -2382,7 +2370,7 @@
         <v>0.05555555555555555</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2579008702421714</v>
+        <v>0.2579008702421715</v>
       </c>
       <c r="F41" t="n">
         <v>2018</v>
@@ -2390,7 +2378,7 @@
       <c r="G41" t="n">
         <v>4</v>
       </c>
-      <c r="H41" s="2" t="n">
+      <c r="H41" s="1" t="n">
         <v>43102</v>
       </c>
       <c r="I41" t="inlineStr">
@@ -2430,7 +2418,7 @@
         <v>0.807936507936508</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5135253067066553</v>
+        <v>0.5135253067066552</v>
       </c>
       <c r="F42" t="n">
         <v>2019</v>
@@ -2438,7 +2426,7 @@
       <c r="G42" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="2" t="n">
+      <c r="H42" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I42" t="inlineStr">
@@ -2478,7 +2466,7 @@
         <v>0.3095238095238095</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3578577944064745</v>
+        <v>0.3578577944064746</v>
       </c>
       <c r="F43" t="n">
         <v>2019</v>
@@ -2486,7 +2474,7 @@
       <c r="G43" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="2" t="n">
+      <c r="H43" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I43" t="inlineStr">
@@ -2526,7 +2514,7 @@
         <v>0.4253968253968254</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4189024619281101</v>
+        <v>0.4189024619281102</v>
       </c>
       <c r="F44" t="n">
         <v>2019</v>
@@ -2534,7 +2522,7 @@
       <c r="G44" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="2" t="n">
+      <c r="H44" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I44" t="inlineStr">
@@ -2574,7 +2562,7 @@
         <v>0.4095238095238095</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4230169108900504</v>
+        <v>0.4230169108900505</v>
       </c>
       <c r="F45" t="n">
         <v>2019</v>
@@ -2582,7 +2570,7 @@
       <c r="G45" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="2" t="n">
+      <c r="H45" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I45" t="inlineStr">
@@ -2622,7 +2610,7 @@
         <v>0.346031746031746</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4352834033423632</v>
+        <v>0.435283403342363</v>
       </c>
       <c r="F46" t="n">
         <v>2019</v>
@@ -2630,7 +2618,7 @@
       <c r="G46" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="2" t="n">
+      <c r="H46" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I46" t="inlineStr">
@@ -2678,7 +2666,7 @@
       <c r="G47" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="2" t="n">
+      <c r="H47" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I47" t="inlineStr">
@@ -2726,7 +2714,7 @@
       <c r="G48" t="n">
         <v>1</v>
       </c>
-      <c r="H48" s="2" t="n">
+      <c r="H48" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I48" t="inlineStr">
@@ -2766,7 +2754,7 @@
         <v>0.1095238095238095</v>
       </c>
       <c r="E49" t="n">
-        <v>0.3423202378270701</v>
+        <v>0.3423202378270699</v>
       </c>
       <c r="F49" t="n">
         <v>2019</v>
@@ -2774,7 +2762,7 @@
       <c r="G49" t="n">
         <v>1</v>
       </c>
-      <c r="H49" s="2" t="n">
+      <c r="H49" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I49" t="inlineStr">
@@ -2822,7 +2810,7 @@
       <c r="G50" t="n">
         <v>1</v>
       </c>
-      <c r="H50" s="2" t="n">
+      <c r="H50" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I50" t="inlineStr">
@@ -2870,7 +2858,7 @@
       <c r="G51" t="n">
         <v>1</v>
       </c>
-      <c r="H51" s="2" t="n">
+      <c r="H51" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I51" t="inlineStr">
@@ -2918,7 +2906,7 @@
       <c r="G52" t="n">
         <v>2</v>
       </c>
-      <c r="H52" s="2" t="n">
+      <c r="H52" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I52" t="inlineStr">
@@ -2958,7 +2946,7 @@
         <v>0.7126984126984127</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3627114356882777</v>
+        <v>0.3627114356882778</v>
       </c>
       <c r="F53" t="n">
         <v>2019</v>
@@ -2966,7 +2954,7 @@
       <c r="G53" t="n">
         <v>2</v>
       </c>
-      <c r="H53" s="2" t="n">
+      <c r="H53" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I53" t="inlineStr">
@@ -3014,7 +3002,7 @@
       <c r="G54" t="n">
         <v>2</v>
       </c>
-      <c r="H54" s="2" t="n">
+      <c r="H54" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I54" t="inlineStr">
@@ -3062,7 +3050,7 @@
       <c r="G55" t="n">
         <v>2</v>
       </c>
-      <c r="H55" s="2" t="n">
+      <c r="H55" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I55" t="inlineStr">
@@ -3102,7 +3090,7 @@
         <v>0.3825396825396825</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2661078639221632</v>
+        <v>0.2661078639221631</v>
       </c>
       <c r="F56" t="n">
         <v>2019</v>
@@ -3110,7 +3098,7 @@
       <c r="G56" t="n">
         <v>2</v>
       </c>
-      <c r="H56" s="2" t="n">
+      <c r="H56" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I56" t="inlineStr">
@@ -3150,7 +3138,7 @@
         <v>0.2587301587301588</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2773647660829971</v>
+        <v>0.2773647660829972</v>
       </c>
       <c r="F57" t="n">
         <v>2019</v>
@@ -3158,7 +3146,7 @@
       <c r="G57" t="n">
         <v>2</v>
       </c>
-      <c r="H57" s="2" t="n">
+      <c r="H57" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I57" t="inlineStr">
@@ -3206,7 +3194,7 @@
       <c r="G58" t="n">
         <v>2</v>
       </c>
-      <c r="H58" s="2" t="n">
+      <c r="H58" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I58" t="inlineStr">
@@ -3254,7 +3242,7 @@
       <c r="G59" t="n">
         <v>2</v>
       </c>
-      <c r="H59" s="2" t="n">
+      <c r="H59" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I59" t="inlineStr">
@@ -3294,7 +3282,7 @@
         <v>0.3857142857142857</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3091209876655078</v>
+        <v>0.3091209876655079</v>
       </c>
       <c r="F60" t="n">
         <v>2019</v>
@@ -3302,7 +3290,7 @@
       <c r="G60" t="n">
         <v>2</v>
       </c>
-      <c r="H60" s="2" t="n">
+      <c r="H60" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I60" t="inlineStr">
@@ -3350,7 +3338,7 @@
       <c r="G61" t="n">
         <v>2</v>
       </c>
-      <c r="H61" s="2" t="n">
+      <c r="H61" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I61" t="inlineStr">
@@ -3398,7 +3386,7 @@
       <c r="G62" t="n">
         <v>3</v>
       </c>
-      <c r="H62" s="2" t="n">
+      <c r="H62" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I62" t="inlineStr">
@@ -3446,7 +3434,7 @@
       <c r="G63" t="n">
         <v>3</v>
       </c>
-      <c r="H63" s="2" t="n">
+      <c r="H63" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I63" t="inlineStr">
@@ -3494,7 +3482,7 @@
       <c r="G64" t="n">
         <v>3</v>
       </c>
-      <c r="H64" s="2" t="n">
+      <c r="H64" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I64" t="inlineStr">
@@ -3542,7 +3530,7 @@
       <c r="G65" t="n">
         <v>3</v>
       </c>
-      <c r="H65" s="2" t="n">
+      <c r="H65" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I65" t="inlineStr">
@@ -3590,7 +3578,7 @@
       <c r="G66" t="n">
         <v>3</v>
       </c>
-      <c r="H66" s="2" t="n">
+      <c r="H66" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I66" t="inlineStr">
@@ -3638,7 +3626,7 @@
       <c r="G67" t="n">
         <v>3</v>
       </c>
-      <c r="H67" s="2" t="n">
+      <c r="H67" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I67" t="inlineStr">
@@ -3678,7 +3666,7 @@
         <v>0.4936507936507937</v>
       </c>
       <c r="E68" t="n">
-        <v>0.2174132638130112</v>
+        <v>0.2174132638130111</v>
       </c>
       <c r="F68" t="n">
         <v>2019</v>
@@ -3686,7 +3674,7 @@
       <c r="G68" t="n">
         <v>3</v>
       </c>
-      <c r="H68" s="2" t="n">
+      <c r="H68" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I68" t="inlineStr">
@@ -3726,7 +3714,7 @@
         <v>0.4523809523809524</v>
       </c>
       <c r="E69" t="n">
-        <v>0.2014329443978565</v>
+        <v>0.2014329443978564</v>
       </c>
       <c r="F69" t="n">
         <v>2019</v>
@@ -3734,7 +3722,7 @@
       <c r="G69" t="n">
         <v>3</v>
       </c>
-      <c r="H69" s="2" t="n">
+      <c r="H69" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I69" t="inlineStr">
@@ -3782,7 +3770,7 @@
       <c r="G70" t="n">
         <v>3</v>
       </c>
-      <c r="H70" s="2" t="n">
+      <c r="H70" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I70" t="inlineStr">
@@ -3830,7 +3818,7 @@
       <c r="G71" t="n">
         <v>3</v>
       </c>
-      <c r="H71" s="2" t="n">
+      <c r="H71" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I71" t="inlineStr">
@@ -3878,7 +3866,7 @@
       <c r="G72" t="n">
         <v>4</v>
       </c>
-      <c r="H72" s="2" t="n">
+      <c r="H72" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I72" t="inlineStr">
@@ -3926,7 +3914,7 @@
       <c r="G73" t="n">
         <v>4</v>
       </c>
-      <c r="H73" s="2" t="n">
+      <c r="H73" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I73" t="inlineStr">
@@ -3966,7 +3954,7 @@
         <v>0.3888888888888889</v>
       </c>
       <c r="E74" t="n">
-        <v>0.2209973943070626</v>
+        <v>0.2209973943070625</v>
       </c>
       <c r="F74" t="n">
         <v>2019</v>
@@ -3974,7 +3962,7 @@
       <c r="G74" t="n">
         <v>4</v>
       </c>
-      <c r="H74" s="2" t="n">
+      <c r="H74" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I74" t="inlineStr">
@@ -4014,7 +4002,7 @@
         <v>0.3476190476190476</v>
       </c>
       <c r="E75" t="n">
-        <v>0.1544752726027461</v>
+        <v>0.154475272602746</v>
       </c>
       <c r="F75" t="n">
         <v>2019</v>
@@ -4022,7 +4010,7 @@
       <c r="G75" t="n">
         <v>4</v>
       </c>
-      <c r="H75" s="2" t="n">
+      <c r="H75" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I75" t="inlineStr">
@@ -4070,7 +4058,7 @@
       <c r="G76" t="n">
         <v>4</v>
       </c>
-      <c r="H76" s="2" t="n">
+      <c r="H76" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I76" t="inlineStr">
@@ -4118,7 +4106,7 @@
       <c r="G77" t="n">
         <v>4</v>
       </c>
-      <c r="H77" s="2" t="n">
+      <c r="H77" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I77" t="inlineStr">
@@ -4166,7 +4154,7 @@
       <c r="G78" t="n">
         <v>4</v>
       </c>
-      <c r="H78" s="2" t="n">
+      <c r="H78" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I78" t="inlineStr">
@@ -4206,7 +4194,7 @@
         <v>0.4365079365079365</v>
       </c>
       <c r="E79" t="n">
-        <v>0.2420338266832113</v>
+        <v>0.2420338266832114</v>
       </c>
       <c r="F79" t="n">
         <v>2019</v>
@@ -4214,7 +4202,7 @@
       <c r="G79" t="n">
         <v>4</v>
       </c>
-      <c r="H79" s="2" t="n">
+      <c r="H79" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I79" t="inlineStr">
@@ -4262,7 +4250,7 @@
       <c r="G80" t="n">
         <v>4</v>
       </c>
-      <c r="H80" s="2" t="n">
+      <c r="H80" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I80" t="inlineStr">
@@ -4302,7 +4290,7 @@
         <v>0.3857142857142857</v>
       </c>
       <c r="E81" t="n">
-        <v>0.1948452415316836</v>
+        <v>0.1948452415316835</v>
       </c>
       <c r="F81" t="n">
         <v>2019</v>
@@ -4310,7 +4298,7 @@
       <c r="G81" t="n">
         <v>4</v>
       </c>
-      <c r="H81" s="2" t="n">
+      <c r="H81" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="I81" t="inlineStr">
@@ -4358,7 +4346,7 @@
       <c r="G82" t="n">
         <v>1</v>
       </c>
-      <c r="H82" s="2" t="n">
+      <c r="H82" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I82" t="inlineStr">
@@ -4406,7 +4394,7 @@
       <c r="G83" t="n">
         <v>1</v>
       </c>
-      <c r="H83" s="2" t="n">
+      <c r="H83" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I83" t="inlineStr">
@@ -4446,7 +4434,7 @@
         <v>0.4777777777777778</v>
       </c>
       <c r="E84" t="n">
-        <v>0.3129847077285028</v>
+        <v>0.3129847077285027</v>
       </c>
       <c r="F84" t="n">
         <v>2020</v>
@@ -4454,7 +4442,7 @@
       <c r="G84" t="n">
         <v>1</v>
       </c>
-      <c r="H84" s="2" t="n">
+      <c r="H84" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I84" t="inlineStr">
@@ -4502,7 +4490,7 @@
       <c r="G85" t="n">
         <v>1</v>
       </c>
-      <c r="H85" s="2" t="n">
+      <c r="H85" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I85" t="inlineStr">
@@ -4550,7 +4538,7 @@
       <c r="G86" t="n">
         <v>1</v>
       </c>
-      <c r="H86" s="2" t="n">
+      <c r="H86" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I86" t="inlineStr">
@@ -4590,7 +4578,7 @@
         <v>0.1603174603174603</v>
       </c>
       <c r="E87" t="n">
-        <v>0.3157339462693672</v>
+        <v>0.3157339462693673</v>
       </c>
       <c r="F87" t="n">
         <v>2020</v>
@@ -4598,7 +4586,7 @@
       <c r="G87" t="n">
         <v>1</v>
       </c>
-      <c r="H87" s="2" t="n">
+      <c r="H87" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I87" t="inlineStr">
@@ -4646,7 +4634,7 @@
       <c r="G88" t="n">
         <v>1</v>
       </c>
-      <c r="H88" s="2" t="n">
+      <c r="H88" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I88" t="inlineStr">
@@ -4686,7 +4674,7 @@
         <v>0.1095238095238095</v>
       </c>
       <c r="E89" t="n">
-        <v>0.2944426124973927</v>
+        <v>0.2944426124973928</v>
       </c>
       <c r="F89" t="n">
         <v>2020</v>
@@ -4694,7 +4682,7 @@
       <c r="G89" t="n">
         <v>1</v>
       </c>
-      <c r="H89" s="2" t="n">
+      <c r="H89" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I89" t="inlineStr">
@@ -4742,7 +4730,7 @@
       <c r="G90" t="n">
         <v>1</v>
       </c>
-      <c r="H90" s="2" t="n">
+      <c r="H90" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I90" t="inlineStr">
@@ -4790,7 +4778,7 @@
       <c r="G91" t="n">
         <v>1</v>
       </c>
-      <c r="H91" s="2" t="n">
+      <c r="H91" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I91" t="inlineStr">
@@ -4838,7 +4826,7 @@
       <c r="G92" t="n">
         <v>2</v>
       </c>
-      <c r="H92" s="2" t="n">
+      <c r="H92" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I92" t="inlineStr">
@@ -4886,7 +4874,7 @@
       <c r="G93" t="n">
         <v>2</v>
       </c>
-      <c r="H93" s="2" t="n">
+      <c r="H93" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I93" t="inlineStr">
@@ -4926,7 +4914,7 @@
         <v>0.3523809523809524</v>
       </c>
       <c r="E94" t="n">
-        <v>0.2188756429604233</v>
+        <v>0.2188756429604234</v>
       </c>
       <c r="F94" t="n">
         <v>2020</v>
@@ -4934,7 +4922,7 @@
       <c r="G94" t="n">
         <v>2</v>
       </c>
-      <c r="H94" s="2" t="n">
+      <c r="H94" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I94" t="inlineStr">
@@ -4982,7 +4970,7 @@
       <c r="G95" t="n">
         <v>2</v>
       </c>
-      <c r="H95" s="2" t="n">
+      <c r="H95" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I95" t="inlineStr">
@@ -5022,7 +5010,7 @@
         <v>0.4666666666666667</v>
       </c>
       <c r="E96" t="n">
-        <v>0.2941047927399894</v>
+        <v>0.2941047927399895</v>
       </c>
       <c r="F96" t="n">
         <v>2020</v>
@@ -5030,7 +5018,7 @@
       <c r="G96" t="n">
         <v>2</v>
       </c>
-      <c r="H96" s="2" t="n">
+      <c r="H96" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I96" t="inlineStr">
@@ -5078,7 +5066,7 @@
       <c r="G97" t="n">
         <v>2</v>
       </c>
-      <c r="H97" s="2" t="n">
+      <c r="H97" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I97" t="inlineStr">
@@ -5126,7 +5114,7 @@
       <c r="G98" t="n">
         <v>2</v>
       </c>
-      <c r="H98" s="2" t="n">
+      <c r="H98" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I98" t="inlineStr">
@@ -5166,7 +5154,7 @@
         <v>0.1603174603174603</v>
       </c>
       <c r="E99" t="n">
-        <v>0.2621916937773258</v>
+        <v>0.2621916937773259</v>
       </c>
       <c r="F99" t="n">
         <v>2020</v>
@@ -5174,7 +5162,7 @@
       <c r="G99" t="n">
         <v>2</v>
       </c>
-      <c r="H99" s="2" t="n">
+      <c r="H99" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I99" t="inlineStr">
@@ -5214,7 +5202,7 @@
         <v>0.3555555555555556</v>
       </c>
       <c r="E100" t="n">
-        <v>0.2523068904420114</v>
+        <v>0.2523068904420113</v>
       </c>
       <c r="F100" t="n">
         <v>2020</v>
@@ -5222,7 +5210,7 @@
       <c r="G100" t="n">
         <v>2</v>
       </c>
-      <c r="H100" s="2" t="n">
+      <c r="H100" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I100" t="inlineStr">
@@ -5270,7 +5258,7 @@
       <c r="G101" t="n">
         <v>2</v>
       </c>
-      <c r="H101" s="2" t="n">
+      <c r="H101" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I101" t="inlineStr">
@@ -5310,7 +5298,7 @@
         <v>0.353968253968254</v>
       </c>
       <c r="E102" t="n">
-        <v>0.2253243015477455</v>
+        <v>0.2253243015477456</v>
       </c>
       <c r="F102" t="n">
         <v>2020</v>
@@ -5318,7 +5306,7 @@
       <c r="G102" t="n">
         <v>3</v>
       </c>
-      <c r="H102" s="2" t="n">
+      <c r="H102" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I102" t="inlineStr">
@@ -5358,7 +5346,7 @@
         <v>0.8015873015873016</v>
       </c>
       <c r="E103" t="n">
-        <v>0.3383835677109478</v>
+        <v>0.3383835677109477</v>
       </c>
       <c r="F103" t="n">
         <v>2020</v>
@@ -5366,7 +5354,7 @@
       <c r="G103" t="n">
         <v>3</v>
       </c>
-      <c r="H103" s="2" t="n">
+      <c r="H103" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I103" t="inlineStr">
@@ -5414,7 +5402,7 @@
       <c r="G104" t="n">
         <v>3</v>
       </c>
-      <c r="H104" s="2" t="n">
+      <c r="H104" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I104" t="inlineStr">
@@ -5462,7 +5450,7 @@
       <c r="G105" t="n">
         <v>3</v>
       </c>
-      <c r="H105" s="2" t="n">
+      <c r="H105" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I105" t="inlineStr">
@@ -5510,7 +5498,7 @@
       <c r="G106" t="n">
         <v>3</v>
       </c>
-      <c r="H106" s="2" t="n">
+      <c r="H106" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I106" t="inlineStr">
@@ -5550,7 +5538,7 @@
         <v>0.3746031746031746</v>
       </c>
       <c r="E107" t="n">
-        <v>0.2839949244477629</v>
+        <v>0.2839949244477628</v>
       </c>
       <c r="F107" t="n">
         <v>2020</v>
@@ -5558,7 +5546,7 @@
       <c r="G107" t="n">
         <v>3</v>
       </c>
-      <c r="H107" s="2" t="n">
+      <c r="H107" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I107" t="inlineStr">
@@ -5606,7 +5594,7 @@
       <c r="G108" t="n">
         <v>3</v>
       </c>
-      <c r="H108" s="2" t="n">
+      <c r="H108" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I108" t="inlineStr">
@@ -5654,7 +5642,7 @@
       <c r="G109" t="n">
         <v>3</v>
       </c>
-      <c r="H109" s="2" t="n">
+      <c r="H109" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I109" t="inlineStr">
@@ -5702,7 +5690,7 @@
       <c r="G110" t="n">
         <v>3</v>
       </c>
-      <c r="H110" s="2" t="n">
+      <c r="H110" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I110" t="inlineStr">
@@ -5750,7 +5738,7 @@
       <c r="G111" t="n">
         <v>3</v>
       </c>
-      <c r="H111" s="2" t="n">
+      <c r="H111" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I111" t="inlineStr">
@@ -5790,7 +5778,7 @@
         <v>0.7063492063492064</v>
       </c>
       <c r="E112" t="n">
-        <v>0.3207403063970953</v>
+        <v>0.3207403063970954</v>
       </c>
       <c r="F112" t="n">
         <v>2020</v>
@@ -5798,7 +5786,7 @@
       <c r="G112" t="n">
         <v>4</v>
       </c>
-      <c r="H112" s="2" t="n">
+      <c r="H112" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I112" t="inlineStr">
@@ -5838,7 +5826,7 @@
         <v>0.353968253968254</v>
       </c>
       <c r="E113" t="n">
-        <v>0.2289242572776205</v>
+        <v>0.2289242572776206</v>
       </c>
       <c r="F113" t="n">
         <v>2020</v>
@@ -5846,7 +5834,7 @@
       <c r="G113" t="n">
         <v>4</v>
       </c>
-      <c r="H113" s="2" t="n">
+      <c r="H113" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I113" t="inlineStr">
@@ -5894,7 +5882,7 @@
       <c r="G114" t="n">
         <v>4</v>
       </c>
-      <c r="H114" s="2" t="n">
+      <c r="H114" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I114" t="inlineStr">
@@ -5942,7 +5930,7 @@
       <c r="G115" t="n">
         <v>4</v>
       </c>
-      <c r="H115" s="2" t="n">
+      <c r="H115" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I115" t="inlineStr">
@@ -5990,7 +5978,7 @@
       <c r="G116" t="n">
         <v>4</v>
       </c>
-      <c r="H116" s="2" t="n">
+      <c r="H116" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I116" t="inlineStr">
@@ -6038,7 +6026,7 @@
       <c r="G117" t="n">
         <v>4</v>
       </c>
-      <c r="H117" s="2" t="n">
+      <c r="H117" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I117" t="inlineStr">
@@ -6086,7 +6074,7 @@
       <c r="G118" t="n">
         <v>4</v>
       </c>
-      <c r="H118" s="2" t="n">
+      <c r="H118" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I118" t="inlineStr">
@@ -6134,7 +6122,7 @@
       <c r="G119" t="n">
         <v>4</v>
       </c>
-      <c r="H119" s="2" t="n">
+      <c r="H119" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I119" t="inlineStr">
@@ -6182,7 +6170,7 @@
       <c r="G120" t="n">
         <v>4</v>
       </c>
-      <c r="H120" s="2" t="n">
+      <c r="H120" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I120" t="inlineStr">
@@ -6230,7 +6218,7 @@
       <c r="G121" t="n">
         <v>4</v>
       </c>
-      <c r="H121" s="2" t="n">
+      <c r="H121" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="I121" t="inlineStr">
@@ -6270,7 +6258,7 @@
         <v>0.7698412698412699</v>
       </c>
       <c r="E122" t="n">
-        <v>0.4720036052315588</v>
+        <v>0.4720036052315589</v>
       </c>
       <c r="F122" t="n">
         <v>2021</v>
@@ -6278,7 +6266,7 @@
       <c r="G122" t="n">
         <v>1</v>
       </c>
-      <c r="H122" s="2" t="n">
+      <c r="H122" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I122" t="inlineStr">
@@ -6318,7 +6306,7 @@
         <v>0.3936507936507936</v>
       </c>
       <c r="E123" t="n">
-        <v>0.341195976520437</v>
+        <v>0.3411959765204368</v>
       </c>
       <c r="F123" t="n">
         <v>2021</v>
@@ -6326,7 +6314,7 @@
       <c r="G123" t="n">
         <v>1</v>
       </c>
-      <c r="H123" s="2" t="n">
+      <c r="H123" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I123" t="inlineStr">
@@ -6366,7 +6354,7 @@
         <v>0.546031746031746</v>
       </c>
       <c r="E124" t="n">
-        <v>0.4420371973657181</v>
+        <v>0.442037197365718</v>
       </c>
       <c r="F124" t="n">
         <v>2021</v>
@@ -6374,7 +6362,7 @@
       <c r="G124" t="n">
         <v>1</v>
       </c>
-      <c r="H124" s="2" t="n">
+      <c r="H124" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I124" t="inlineStr">
@@ -6422,7 +6410,7 @@
       <c r="G125" t="n">
         <v>1</v>
       </c>
-      <c r="H125" s="2" t="n">
+      <c r="H125" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I125" t="inlineStr">
@@ -6470,7 +6458,7 @@
       <c r="G126" t="n">
         <v>1</v>
       </c>
-      <c r="H126" s="2" t="n">
+      <c r="H126" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I126" t="inlineStr">
@@ -6518,7 +6506,7 @@
       <c r="G127" t="n">
         <v>1</v>
       </c>
-      <c r="H127" s="2" t="n">
+      <c r="H127" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I127" t="inlineStr">
@@ -6566,7 +6554,7 @@
       <c r="G128" t="n">
         <v>1</v>
       </c>
-      <c r="H128" s="2" t="n">
+      <c r="H128" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I128" t="inlineStr">
@@ -6614,7 +6602,7 @@
       <c r="G129" t="n">
         <v>1</v>
       </c>
-      <c r="H129" s="2" t="n">
+      <c r="H129" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I129" t="inlineStr">
@@ -6662,7 +6650,7 @@
       <c r="G130" t="n">
         <v>1</v>
       </c>
-      <c r="H130" s="2" t="n">
+      <c r="H130" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I130" t="inlineStr">
@@ -6702,7 +6690,7 @@
         <v>0.1079365079365079</v>
       </c>
       <c r="E131" t="n">
-        <v>0.3705153730489675</v>
+        <v>0.3705153730489676</v>
       </c>
       <c r="F131" t="n">
         <v>2021</v>
@@ -6710,7 +6698,7 @@
       <c r="G131" t="n">
         <v>1</v>
       </c>
-      <c r="H131" s="2" t="n">
+      <c r="H131" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I131" t="inlineStr">
@@ -6758,7 +6746,7 @@
       <c r="G132" t="n">
         <v>2</v>
       </c>
-      <c r="H132" s="2" t="n">
+      <c r="H132" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I132" t="inlineStr">
@@ -6798,7 +6786,7 @@
         <v>0.7396825396825397</v>
       </c>
       <c r="E133" t="n">
-        <v>0.3451969777104408</v>
+        <v>0.3451969777104409</v>
       </c>
       <c r="F133" t="n">
         <v>2021</v>
@@ -6806,7 +6794,7 @@
       <c r="G133" t="n">
         <v>2</v>
       </c>
-      <c r="H133" s="2" t="n">
+      <c r="H133" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I133" t="inlineStr">
@@ -6854,7 +6842,7 @@
       <c r="G134" t="n">
         <v>2</v>
       </c>
-      <c r="H134" s="2" t="n">
+      <c r="H134" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I134" t="inlineStr">
@@ -6894,7 +6882,7 @@
         <v>0.2111111111111111</v>
       </c>
       <c r="E135" t="n">
-        <v>0.2668562666985674</v>
+        <v>0.2668562666985675</v>
       </c>
       <c r="F135" t="n">
         <v>2021</v>
@@ -6902,7 +6890,7 @@
       <c r="G135" t="n">
         <v>2</v>
       </c>
-      <c r="H135" s="2" t="n">
+      <c r="H135" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I135" t="inlineStr">
@@ -6950,7 +6938,7 @@
       <c r="G136" t="n">
         <v>2</v>
       </c>
-      <c r="H136" s="2" t="n">
+      <c r="H136" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I136" t="inlineStr">
@@ -6990,7 +6978,7 @@
         <v>0.2984126984126984</v>
       </c>
       <c r="E137" t="n">
-        <v>0.2414888758672637</v>
+        <v>0.2414888758672636</v>
       </c>
       <c r="F137" t="n">
         <v>2021</v>
@@ -6998,7 +6986,7 @@
       <c r="G137" t="n">
         <v>2</v>
       </c>
-      <c r="H137" s="2" t="n">
+      <c r="H137" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I137" t="inlineStr">
@@ -7038,7 +7026,7 @@
         <v>0.1603174603174603</v>
       </c>
       <c r="E138" t="n">
-        <v>0.2015669045082743</v>
+        <v>0.2015669045082742</v>
       </c>
       <c r="F138" t="n">
         <v>2021</v>
@@ -7046,7 +7034,7 @@
       <c r="G138" t="n">
         <v>2</v>
       </c>
-      <c r="H138" s="2" t="n">
+      <c r="H138" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I138" t="inlineStr">
@@ -7094,7 +7082,7 @@
       <c r="G139" t="n">
         <v>2</v>
       </c>
-      <c r="H139" s="2" t="n">
+      <c r="H139" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I139" t="inlineStr">
@@ -7134,7 +7122,7 @@
         <v>0.4126984126984127</v>
       </c>
       <c r="E140" t="n">
-        <v>0.302937716906734</v>
+        <v>0.3029377169067339</v>
       </c>
       <c r="F140" t="n">
         <v>2021</v>
@@ -7142,7 +7130,7 @@
       <c r="G140" t="n">
         <v>2</v>
       </c>
-      <c r="H140" s="2" t="n">
+      <c r="H140" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I140" t="inlineStr">
@@ -7182,7 +7170,7 @@
         <v>0.3857142857142857</v>
       </c>
       <c r="E141" t="n">
-        <v>0.2634896166301801</v>
+        <v>0.26348961663018</v>
       </c>
       <c r="F141" t="n">
         <v>2021</v>
@@ -7190,7 +7178,7 @@
       <c r="G141" t="n">
         <v>2</v>
       </c>
-      <c r="H141" s="2" t="n">
+      <c r="H141" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I141" t="inlineStr">
@@ -7238,7 +7226,7 @@
       <c r="G142" t="n">
         <v>3</v>
       </c>
-      <c r="H142" s="2" t="n">
+      <c r="H142" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I142" t="inlineStr">
@@ -7278,7 +7266,7 @@
         <v>0.4555555555555555</v>
       </c>
       <c r="E143" t="n">
-        <v>0.2719555622302047</v>
+        <v>0.2719555622302046</v>
       </c>
       <c r="F143" t="n">
         <v>2021</v>
@@ -7286,7 +7274,7 @@
       <c r="G143" t="n">
         <v>3</v>
       </c>
-      <c r="H143" s="2" t="n">
+      <c r="H143" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I143" t="inlineStr">
@@ -7326,7 +7314,7 @@
         <v>0.2571428571428571</v>
       </c>
       <c r="E144" t="n">
-        <v>0.2639746122937917</v>
+        <v>0.2639746122937918</v>
       </c>
       <c r="F144" t="n">
         <v>2021</v>
@@ -7334,7 +7322,7 @@
       <c r="G144" t="n">
         <v>3</v>
       </c>
-      <c r="H144" s="2" t="n">
+      <c r="H144" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I144" t="inlineStr">
@@ -7382,7 +7370,7 @@
       <c r="G145" t="n">
         <v>3</v>
       </c>
-      <c r="H145" s="2" t="n">
+      <c r="H145" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I145" t="inlineStr">
@@ -7430,7 +7418,7 @@
       <c r="G146" t="n">
         <v>3</v>
       </c>
-      <c r="H146" s="2" t="n">
+      <c r="H146" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I146" t="inlineStr">
@@ -7478,7 +7466,7 @@
       <c r="G147" t="n">
         <v>3</v>
       </c>
-      <c r="H147" s="2" t="n">
+      <c r="H147" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I147" t="inlineStr">
@@ -7526,7 +7514,7 @@
       <c r="G148" t="n">
         <v>3</v>
       </c>
-      <c r="H148" s="2" t="n">
+      <c r="H148" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I148" t="inlineStr">
@@ -7574,7 +7562,7 @@
       <c r="G149" t="n">
         <v>3</v>
       </c>
-      <c r="H149" s="2" t="n">
+      <c r="H149" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I149" t="inlineStr">
@@ -7614,7 +7602,7 @@
         <v>0.1095238095238095</v>
       </c>
       <c r="E150" t="n">
-        <v>0.2279248917331645</v>
+        <v>0.2279248917331644</v>
       </c>
       <c r="F150" t="n">
         <v>2021</v>
@@ -7622,7 +7610,7 @@
       <c r="G150" t="n">
         <v>3</v>
       </c>
-      <c r="H150" s="2" t="n">
+      <c r="H150" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I150" t="inlineStr">
@@ -7670,7 +7658,7 @@
       <c r="G151" t="n">
         <v>3</v>
       </c>
-      <c r="H151" s="2" t="n">
+      <c r="H151" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I151" t="inlineStr">
@@ -7710,7 +7698,7 @@
         <v>0.5174603174603175</v>
       </c>
       <c r="E152" t="n">
-        <v>0.2343533547774498</v>
+        <v>0.2343533547774499</v>
       </c>
       <c r="F152" t="n">
         <v>2021</v>
@@ -7718,7 +7706,7 @@
       <c r="G152" t="n">
         <v>4</v>
       </c>
-      <c r="H152" s="2" t="n">
+      <c r="H152" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I152" t="inlineStr">
@@ -7766,7 +7754,7 @@
       <c r="G153" t="n">
         <v>4</v>
       </c>
-      <c r="H153" s="2" t="n">
+      <c r="H153" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I153" t="inlineStr">
@@ -7814,7 +7802,7 @@
       <c r="G154" t="n">
         <v>4</v>
       </c>
-      <c r="H154" s="2" t="n">
+      <c r="H154" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I154" t="inlineStr">
@@ -7862,7 +7850,7 @@
       <c r="G155" t="n">
         <v>4</v>
       </c>
-      <c r="H155" s="2" t="n">
+      <c r="H155" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I155" t="inlineStr">
@@ -7910,7 +7898,7 @@
       <c r="G156" t="n">
         <v>4</v>
       </c>
-      <c r="H156" s="2" t="n">
+      <c r="H156" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I156" t="inlineStr">
@@ -7958,7 +7946,7 @@
       <c r="G157" t="n">
         <v>4</v>
       </c>
-      <c r="H157" s="2" t="n">
+      <c r="H157" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I157" t="inlineStr">
@@ -8006,7 +7994,7 @@
       <c r="G158" t="n">
         <v>4</v>
       </c>
-      <c r="H158" s="2" t="n">
+      <c r="H158" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I158" t="inlineStr">
@@ -8054,7 +8042,7 @@
       <c r="G159" t="n">
         <v>4</v>
       </c>
-      <c r="H159" s="2" t="n">
+      <c r="H159" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I159" t="inlineStr">
@@ -8102,7 +8090,7 @@
       <c r="G160" t="n">
         <v>4</v>
       </c>
-      <c r="H160" s="2" t="n">
+      <c r="H160" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I160" t="inlineStr">
@@ -8142,7 +8130,7 @@
         <v>0.1079365079365079</v>
       </c>
       <c r="E161" t="n">
-        <v>0.2132267382707393</v>
+        <v>0.2132267382707394</v>
       </c>
       <c r="F161" t="n">
         <v>2021</v>
@@ -8150,7 +8138,7 @@
       <c r="G161" t="n">
         <v>4</v>
       </c>
-      <c r="H161" s="2" t="n">
+      <c r="H161" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="I161" t="inlineStr">
@@ -8190,7 +8178,7 @@
         <v>0.7587301587301587</v>
       </c>
       <c r="E162" t="n">
-        <v>0.4787297519689299</v>
+        <v>0.4787297519689298</v>
       </c>
       <c r="F162" t="n">
         <v>2022</v>
@@ -8198,7 +8186,7 @@
       <c r="G162" t="n">
         <v>1</v>
       </c>
-      <c r="H162" s="2" t="n">
+      <c r="H162" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I162" t="inlineStr">
@@ -8246,7 +8234,7 @@
       <c r="G163" t="n">
         <v>1</v>
       </c>
-      <c r="H163" s="2" t="n">
+      <c r="H163" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I163" t="inlineStr">
@@ -8294,7 +8282,7 @@
       <c r="G164" t="n">
         <v>1</v>
       </c>
-      <c r="H164" s="2" t="n">
+      <c r="H164" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I164" t="inlineStr">
@@ -8334,7 +8322,7 @@
         <v>0.4936507936507937</v>
       </c>
       <c r="E165" t="n">
-        <v>0.4409121128149948</v>
+        <v>0.4409121128149947</v>
       </c>
       <c r="F165" t="n">
         <v>2022</v>
@@ -8342,7 +8330,7 @@
       <c r="G165" t="n">
         <v>1</v>
       </c>
-      <c r="H165" s="2" t="n">
+      <c r="H165" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I165" t="inlineStr">
@@ -8382,7 +8370,7 @@
         <v>0.4523809523809524</v>
       </c>
       <c r="E166" t="n">
-        <v>0.389810562421276</v>
+        <v>0.3898105624212761</v>
       </c>
       <c r="F166" t="n">
         <v>2022</v>
@@ -8390,7 +8378,7 @@
       <c r="G166" t="n">
         <v>1</v>
       </c>
-      <c r="H166" s="2" t="n">
+      <c r="H166" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I166" t="inlineStr">
@@ -8438,7 +8426,7 @@
       <c r="G167" t="n">
         <v>1</v>
       </c>
-      <c r="H167" s="2" t="n">
+      <c r="H167" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I167" t="inlineStr">
@@ -8478,7 +8466,7 @@
         <v>0.1095238095238095</v>
       </c>
       <c r="E168" t="n">
-        <v>0.3390043165039535</v>
+        <v>0.3390043165039534</v>
       </c>
       <c r="F168" t="n">
         <v>2022</v>
@@ -8486,7 +8474,7 @@
       <c r="G168" t="n">
         <v>1</v>
       </c>
-      <c r="H168" s="2" t="n">
+      <c r="H168" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I168" t="inlineStr">
@@ -8526,7 +8514,7 @@
         <v>0.1095238095238095</v>
       </c>
       <c r="E169" t="n">
-        <v>0.2868515709769621</v>
+        <v>0.2868515709769622</v>
       </c>
       <c r="F169" t="n">
         <v>2022</v>
@@ -8534,7 +8522,7 @@
       <c r="G169" t="n">
         <v>1</v>
       </c>
-      <c r="H169" s="2" t="n">
+      <c r="H169" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I169" t="inlineStr">
@@ -8574,7 +8562,7 @@
         <v>0.1095238095238095</v>
       </c>
       <c r="E170" t="n">
-        <v>0.2699030849875322</v>
+        <v>0.2699030849875321</v>
       </c>
       <c r="F170" t="n">
         <v>2022</v>
@@ -8582,7 +8570,7 @@
       <c r="G170" t="n">
         <v>1</v>
       </c>
-      <c r="H170" s="2" t="n">
+      <c r="H170" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I170" t="inlineStr">
@@ -8630,7 +8618,7 @@
       <c r="G171" t="n">
         <v>1</v>
       </c>
-      <c r="H171" s="2" t="n">
+      <c r="H171" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I171" t="inlineStr">
@@ -8670,7 +8658,7 @@
         <v>0.7634920634920634</v>
       </c>
       <c r="E172" t="n">
-        <v>0.3295582798086987</v>
+        <v>0.3295582798086988</v>
       </c>
       <c r="F172" t="n">
         <v>2022</v>
@@ -8678,7 +8666,7 @@
       <c r="G172" t="n">
         <v>2</v>
       </c>
-      <c r="H172" s="2" t="n">
+      <c r="H172" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I172" t="inlineStr">
@@ -8726,7 +8714,7 @@
       <c r="G173" t="n">
         <v>2</v>
       </c>
-      <c r="H173" s="2" t="n">
+      <c r="H173" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I173" t="inlineStr">
@@ -8774,7 +8762,7 @@
       <c r="G174" t="n">
         <v>2</v>
       </c>
-      <c r="H174" s="2" t="n">
+      <c r="H174" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I174" t="inlineStr">
@@ -8822,7 +8810,7 @@
       <c r="G175" t="n">
         <v>2</v>
       </c>
-      <c r="H175" s="2" t="n">
+      <c r="H175" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I175" t="inlineStr">
@@ -8870,7 +8858,7 @@
       <c r="G176" t="n">
         <v>2</v>
       </c>
-      <c r="H176" s="2" t="n">
+      <c r="H176" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I176" t="inlineStr">
@@ -8918,7 +8906,7 @@
       <c r="G177" t="n">
         <v>2</v>
       </c>
-      <c r="H177" s="2" t="n">
+      <c r="H177" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I177" t="inlineStr">
@@ -8966,7 +8954,7 @@
       <c r="G178" t="n">
         <v>2</v>
       </c>
-      <c r="H178" s="2" t="n">
+      <c r="H178" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I178" t="inlineStr">
@@ -9014,7 +9002,7 @@
       <c r="G179" t="n">
         <v>2</v>
       </c>
-      <c r="H179" s="2" t="n">
+      <c r="H179" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I179" t="inlineStr">
@@ -9062,7 +9050,7 @@
       <c r="G180" t="n">
         <v>2</v>
       </c>
-      <c r="H180" s="2" t="n">
+      <c r="H180" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I180" t="inlineStr">
@@ -9110,7 +9098,7 @@
       <c r="G181" t="n">
         <v>2</v>
       </c>
-      <c r="H181" s="2" t="n">
+      <c r="H181" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I181" t="inlineStr">
@@ -9158,7 +9146,7 @@
       <c r="G182" t="n">
         <v>3</v>
       </c>
-      <c r="H182" s="2" t="n">
+      <c r="H182" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I182" t="inlineStr">
@@ -9206,7 +9194,7 @@
       <c r="G183" t="n">
         <v>3</v>
       </c>
-      <c r="H183" s="2" t="n">
+      <c r="H183" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I183" t="inlineStr">
@@ -9254,7 +9242,7 @@
       <c r="G184" t="n">
         <v>3</v>
       </c>
-      <c r="H184" s="2" t="n">
+      <c r="H184" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I184" t="inlineStr">
@@ -9294,7 +9282,7 @@
         <v>0.1619047619047619</v>
       </c>
       <c r="E185" t="n">
-        <v>0.2515357557321424</v>
+        <v>0.2515357557321423</v>
       </c>
       <c r="F185" t="n">
         <v>2022</v>
@@ -9302,7 +9290,7 @@
       <c r="G185" t="n">
         <v>3</v>
       </c>
-      <c r="H185" s="2" t="n">
+      <c r="H185" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I185" t="inlineStr">
@@ -9350,7 +9338,7 @@
       <c r="G186" t="n">
         <v>3</v>
       </c>
-      <c r="H186" s="2" t="n">
+      <c r="H186" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I186" t="inlineStr">
@@ -9398,7 +9386,7 @@
       <c r="G187" t="n">
         <v>3</v>
       </c>
-      <c r="H187" s="2" t="n">
+      <c r="H187" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I187" t="inlineStr">
@@ -9438,7 +9426,7 @@
         <v>0.2095238095238095</v>
       </c>
       <c r="E188" t="n">
-        <v>0.2636764821104049</v>
+        <v>0.2636764821104048</v>
       </c>
       <c r="F188" t="n">
         <v>2022</v>
@@ -9446,7 +9434,7 @@
       <c r="G188" t="n">
         <v>3</v>
       </c>
-      <c r="H188" s="2" t="n">
+      <c r="H188" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I188" t="inlineStr">
@@ -9494,7 +9482,7 @@
       <c r="G189" t="n">
         <v>3</v>
       </c>
-      <c r="H189" s="2" t="n">
+      <c r="H189" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I189" t="inlineStr">
@@ -9534,7 +9522,7 @@
         <v>0.5126984126984127</v>
       </c>
       <c r="E190" t="n">
-        <v>0.3115585044466029</v>
+        <v>0.311558504446603</v>
       </c>
       <c r="F190" t="n">
         <v>2022</v>
@@ -9542,7 +9530,7 @@
       <c r="G190" t="n">
         <v>3</v>
       </c>
-      <c r="H190" s="2" t="n">
+      <c r="H190" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I190" t="inlineStr">
@@ -9590,7 +9578,7 @@
       <c r="G191" t="n">
         <v>3</v>
       </c>
-      <c r="H191" s="2" t="n">
+      <c r="H191" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I191" t="inlineStr">
@@ -9638,7 +9626,7 @@
       <c r="G192" t="n">
         <v>4</v>
       </c>
-      <c r="H192" s="2" t="n">
+      <c r="H192" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I192" t="inlineStr">
@@ -9678,7 +9666,7 @@
         <v>0.5793650793650794</v>
       </c>
       <c r="E193" t="n">
-        <v>0.3049319596612768</v>
+        <v>0.3049319596612767</v>
       </c>
       <c r="F193" t="n">
         <v>2022</v>
@@ -9686,7 +9674,7 @@
       <c r="G193" t="n">
         <v>4</v>
       </c>
-      <c r="H193" s="2" t="n">
+      <c r="H193" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I193" t="inlineStr">
@@ -9734,7 +9722,7 @@
       <c r="G194" t="n">
         <v>4</v>
       </c>
-      <c r="H194" s="2" t="n">
+      <c r="H194" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I194" t="inlineStr">
@@ -9782,7 +9770,7 @@
       <c r="G195" t="n">
         <v>4</v>
       </c>
-      <c r="H195" s="2" t="n">
+      <c r="H195" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I195" t="inlineStr">
@@ -9830,7 +9818,7 @@
       <c r="G196" t="n">
         <v>4</v>
       </c>
-      <c r="H196" s="2" t="n">
+      <c r="H196" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I196" t="inlineStr">
@@ -9878,7 +9866,7 @@
       <c r="G197" t="n">
         <v>4</v>
       </c>
-      <c r="H197" s="2" t="n">
+      <c r="H197" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I197" t="inlineStr">
@@ -9926,7 +9914,7 @@
       <c r="G198" t="n">
         <v>4</v>
       </c>
-      <c r="H198" s="2" t="n">
+      <c r="H198" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I198" t="inlineStr">
@@ -9966,7 +9954,7 @@
         <v>0.1095238095238095</v>
       </c>
       <c r="E199" t="n">
-        <v>0.16524815802073</v>
+        <v>0.1652481580207299</v>
       </c>
       <c r="F199" t="n">
         <v>2022</v>
@@ -9974,7 +9962,7 @@
       <c r="G199" t="n">
         <v>4</v>
       </c>
-      <c r="H199" s="2" t="n">
+      <c r="H199" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I199" t="inlineStr">
@@ -10014,7 +10002,7 @@
         <v>0.4571428571428571</v>
       </c>
       <c r="E200" t="n">
-        <v>0.294436619114272</v>
+        <v>0.2944366191142719</v>
       </c>
       <c r="F200" t="n">
         <v>2022</v>
@@ -10022,7 +10010,7 @@
       <c r="G200" t="n">
         <v>4</v>
       </c>
-      <c r="H200" s="2" t="n">
+      <c r="H200" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I200" t="inlineStr">
@@ -10070,7 +10058,7 @@
       <c r="G201" t="n">
         <v>4</v>
       </c>
-      <c r="H201" s="2" t="n">
+      <c r="H201" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="I201" t="inlineStr">
@@ -10118,7 +10106,7 @@
       <c r="G202" t="n">
         <v>1</v>
       </c>
-      <c r="H202" s="2" t="n">
+      <c r="H202" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I202" t="inlineStr">
@@ -10158,7 +10146,7 @@
         <v>0.3904761904761905</v>
       </c>
       <c r="E203" t="n">
-        <v>0.3589630188490936</v>
+        <v>0.3589630188490937</v>
       </c>
       <c r="F203" t="n">
         <v>2023</v>
@@ -10166,7 +10154,7 @@
       <c r="G203" t="n">
         <v>1</v>
       </c>
-      <c r="H203" s="2" t="n">
+      <c r="H203" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I203" t="inlineStr">
@@ -10206,7 +10194,7 @@
         <v>0.4666666666666667</v>
       </c>
       <c r="E204" t="n">
-        <v>0.3629884856917658</v>
+        <v>0.3629884856917659</v>
       </c>
       <c r="F204" t="n">
         <v>2023</v>
@@ -10214,7 +10202,7 @@
       <c r="G204" t="n">
         <v>1</v>
       </c>
-      <c r="H204" s="2" t="n">
+      <c r="H204" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I204" t="inlineStr">
@@ -10262,7 +10250,7 @@
       <c r="G205" t="n">
         <v>1</v>
       </c>
-      <c r="H205" s="2" t="n">
+      <c r="H205" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I205" t="inlineStr">
@@ -10310,7 +10298,7 @@
       <c r="G206" t="n">
         <v>1</v>
       </c>
-      <c r="H206" s="2" t="n">
+      <c r="H206" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I206" t="inlineStr">
@@ -10350,7 +10338,7 @@
         <v>0.5603174603174603</v>
       </c>
       <c r="E207" t="n">
-        <v>0.4136373452418294</v>
+        <v>0.4136373452418295</v>
       </c>
       <c r="F207" t="n">
         <v>2023</v>
@@ -10358,7 +10346,7 @@
       <c r="G207" t="n">
         <v>1</v>
       </c>
-      <c r="H207" s="2" t="n">
+      <c r="H207" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I207" t="inlineStr">
@@ -10406,7 +10394,7 @@
       <c r="G208" t="n">
         <v>1</v>
       </c>
-      <c r="H208" s="2" t="n">
+      <c r="H208" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I208" t="inlineStr">
@@ -10446,7 +10434,7 @@
         <v>0.2079365079365079</v>
       </c>
       <c r="E209" t="n">
-        <v>0.3437059591807802</v>
+        <v>0.3437059591807803</v>
       </c>
       <c r="F209" t="n">
         <v>2023</v>
@@ -10454,7 +10442,7 @@
       <c r="G209" t="n">
         <v>1</v>
       </c>
-      <c r="H209" s="2" t="n">
+      <c r="H209" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I209" t="inlineStr">
@@ -10494,7 +10482,7 @@
         <v>0.1571428571428571</v>
       </c>
       <c r="E210" t="n">
-        <v>0.2723866673891632</v>
+        <v>0.2723866673891633</v>
       </c>
       <c r="F210" t="n">
         <v>2023</v>
@@ -10502,7 +10490,7 @@
       <c r="G210" t="n">
         <v>1</v>
       </c>
-      <c r="H210" s="2" t="n">
+      <c r="H210" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I210" t="inlineStr">
@@ -10550,7 +10538,7 @@
       <c r="G211" t="n">
         <v>1</v>
       </c>
-      <c r="H211" s="2" t="n">
+      <c r="H211" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I211" t="inlineStr">
@@ -10590,7 +10578,7 @@
         <v>0.7523809523809524</v>
       </c>
       <c r="E212" t="n">
-        <v>0.3201502621570125</v>
+        <v>0.3201502621570126</v>
       </c>
       <c r="F212" t="n">
         <v>2023</v>
@@ -10598,7 +10586,7 @@
       <c r="G212" t="n">
         <v>2</v>
       </c>
-      <c r="H212" s="2" t="n">
+      <c r="H212" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I212" t="inlineStr">
@@ -10638,7 +10626,7 @@
         <v>0.4777777777777778</v>
       </c>
       <c r="E213" t="n">
-        <v>0.2912543500914542</v>
+        <v>0.2912543500914543</v>
       </c>
       <c r="F213" t="n">
         <v>2023</v>
@@ -10646,7 +10634,7 @@
       <c r="G213" t="n">
         <v>2</v>
       </c>
-      <c r="H213" s="2" t="n">
+      <c r="H213" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I213" t="inlineStr">
@@ -10694,7 +10682,7 @@
       <c r="G214" t="n">
         <v>2</v>
       </c>
-      <c r="H214" s="2" t="n">
+      <c r="H214" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I214" t="inlineStr">
@@ -10742,7 +10730,7 @@
       <c r="G215" t="n">
         <v>2</v>
       </c>
-      <c r="H215" s="2" t="n">
+      <c r="H215" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I215" t="inlineStr">
@@ -10790,7 +10778,7 @@
       <c r="G216" t="n">
         <v>2</v>
       </c>
-      <c r="H216" s="2" t="n">
+      <c r="H216" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I216" t="inlineStr">
@@ -10838,7 +10826,7 @@
       <c r="G217" t="n">
         <v>2</v>
       </c>
-      <c r="H217" s="2" t="n">
+      <c r="H217" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I217" t="inlineStr">
@@ -10886,7 +10874,7 @@
       <c r="G218" t="n">
         <v>2</v>
       </c>
-      <c r="H218" s="2" t="n">
+      <c r="H218" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I218" t="inlineStr">
@@ -10934,7 +10922,7 @@
       <c r="G219" t="n">
         <v>2</v>
       </c>
-      <c r="H219" s="2" t="n">
+      <c r="H219" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I219" t="inlineStr">
@@ -10982,7 +10970,7 @@
       <c r="G220" t="n">
         <v>2</v>
       </c>
-      <c r="H220" s="2" t="n">
+      <c r="H220" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I220" t="inlineStr">
@@ -11030,7 +11018,7 @@
       <c r="G221" t="n">
         <v>2</v>
       </c>
-      <c r="H221" s="2" t="n">
+      <c r="H221" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I221" t="inlineStr">
@@ -11070,7 +11058,7 @@
         <v>0.780952380952381</v>
       </c>
       <c r="E222" t="n">
-        <v>0.3693249504515129</v>
+        <v>0.369324950451513</v>
       </c>
       <c r="F222" t="n">
         <v>2023</v>
@@ -11078,7 +11066,7 @@
       <c r="G222" t="n">
         <v>3</v>
       </c>
-      <c r="H222" s="2" t="n">
+      <c r="H222" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I222" t="inlineStr">
@@ -11126,7 +11114,7 @@
       <c r="G223" t="n">
         <v>3</v>
       </c>
-      <c r="H223" s="2" t="n">
+      <c r="H223" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I223" t="inlineStr">
@@ -11174,7 +11162,7 @@
       <c r="G224" t="n">
         <v>3</v>
       </c>
-      <c r="H224" s="2" t="n">
+      <c r="H224" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I224" t="inlineStr">
@@ -11222,7 +11210,7 @@
       <c r="G225" t="n">
         <v>3</v>
       </c>
-      <c r="H225" s="2" t="n">
+      <c r="H225" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I225" t="inlineStr">
@@ -11270,7 +11258,7 @@
       <c r="G226" t="n">
         <v>3</v>
       </c>
-      <c r="H226" s="2" t="n">
+      <c r="H226" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I226" t="inlineStr">
@@ -11310,7 +11298,7 @@
         <v>0.1603174603174603</v>
       </c>
       <c r="E227" t="n">
-        <v>0.2867758800470414</v>
+        <v>0.2867758800470413</v>
       </c>
       <c r="F227" t="n">
         <v>2023</v>
@@ -11318,7 +11306,7 @@
       <c r="G227" t="n">
         <v>3</v>
       </c>
-      <c r="H227" s="2" t="n">
+      <c r="H227" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I227" t="inlineStr">
@@ -11366,7 +11354,7 @@
       <c r="G228" t="n">
         <v>3</v>
       </c>
-      <c r="H228" s="2" t="n">
+      <c r="H228" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I228" t="inlineStr">
@@ -11414,7 +11402,7 @@
       <c r="G229" t="n">
         <v>3</v>
       </c>
-      <c r="H229" s="2" t="n">
+      <c r="H229" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I229" t="inlineStr">
@@ -11454,7 +11442,7 @@
         <v>0.3555555555555556</v>
       </c>
       <c r="E230" t="n">
-        <v>0.3102338227991378</v>
+        <v>0.3102338227991377</v>
       </c>
       <c r="F230" t="n">
         <v>2023</v>
@@ -11462,7 +11450,7 @@
       <c r="G230" t="n">
         <v>3</v>
       </c>
-      <c r="H230" s="2" t="n">
+      <c r="H230" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I230" t="inlineStr">
@@ -11510,7 +11498,7 @@
       <c r="G231" t="n">
         <v>3</v>
       </c>
-      <c r="H231" s="2" t="n">
+      <c r="H231" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I231" t="inlineStr">
@@ -11558,7 +11546,7 @@
       <c r="G232" t="n">
         <v>4</v>
       </c>
-      <c r="H232" s="2" t="n">
+      <c r="H232" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I232" t="inlineStr">
@@ -11598,7 +11586,7 @@
         <v>0.4634920634920635</v>
       </c>
       <c r="E233" t="n">
-        <v>0.2223571568968503</v>
+        <v>0.2223571568968502</v>
       </c>
       <c r="F233" t="n">
         <v>2023</v>
@@ -11606,7 +11594,7 @@
       <c r="G233" t="n">
         <v>4</v>
       </c>
-      <c r="H233" s="2" t="n">
+      <c r="H233" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I233" t="inlineStr">
@@ -11654,7 +11642,7 @@
       <c r="G234" t="n">
         <v>4</v>
       </c>
-      <c r="H234" s="2" t="n">
+      <c r="H234" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I234" t="inlineStr">
@@ -11702,7 +11690,7 @@
       <c r="G235" t="n">
         <v>4</v>
       </c>
-      <c r="H235" s="2" t="n">
+      <c r="H235" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I235" t="inlineStr">
@@ -11750,7 +11738,7 @@
       <c r="G236" t="n">
         <v>4</v>
       </c>
-      <c r="H236" s="2" t="n">
+      <c r="H236" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I236" t="inlineStr">
@@ -11790,7 +11778,7 @@
         <v>0.2936507936507937</v>
       </c>
       <c r="E237" t="n">
-        <v>0.227983148838199</v>
+        <v>0.2279831488381989</v>
       </c>
       <c r="F237" t="n">
         <v>2023</v>
@@ -11798,7 +11786,7 @@
       <c r="G237" t="n">
         <v>4</v>
       </c>
-      <c r="H237" s="2" t="n">
+      <c r="H237" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I237" t="inlineStr">
@@ -11846,7 +11834,7 @@
       <c r="G238" t="n">
         <v>4</v>
       </c>
-      <c r="H238" s="2" t="n">
+      <c r="H238" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I238" t="inlineStr">
@@ -11894,7 +11882,7 @@
       <c r="G239" t="n">
         <v>4</v>
       </c>
-      <c r="H239" s="2" t="n">
+      <c r="H239" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I239" t="inlineStr">
@@ -11942,7 +11930,7 @@
       <c r="G240" t="n">
         <v>4</v>
       </c>
-      <c r="H240" s="2" t="n">
+      <c r="H240" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I240" t="inlineStr">
@@ -11982,7 +11970,7 @@
         <v>0.1095238095238095</v>
       </c>
       <c r="E241" t="n">
-        <v>0.1823128351959049</v>
+        <v>0.1823128351959048</v>
       </c>
       <c r="F241" t="n">
         <v>2023</v>
@@ -11990,7 +11978,7 @@
       <c r="G241" t="n">
         <v>4</v>
       </c>
-      <c r="H241" s="2" t="n">
+      <c r="H241" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="I241" t="inlineStr">
@@ -12038,7 +12026,7 @@
       <c r="G242" t="n">
         <v>1</v>
       </c>
-      <c r="H242" s="2" t="n">
+      <c r="H242" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I242" t="inlineStr">
@@ -12086,7 +12074,7 @@
       <c r="G243" t="n">
         <v>1</v>
       </c>
-      <c r="H243" s="2" t="n">
+      <c r="H243" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I243" t="inlineStr">
@@ -12126,7 +12114,7 @@
         <v>0.4666666666666667</v>
       </c>
       <c r="E244" t="n">
-        <v>0.35214635843313</v>
+        <v>0.3521463584331301</v>
       </c>
       <c r="F244" t="n">
         <v>2024</v>
@@ -12134,7 +12122,7 @@
       <c r="G244" t="n">
         <v>1</v>
       </c>
-      <c r="H244" s="2" t="n">
+      <c r="H244" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I244" t="inlineStr">
@@ -12182,7 +12170,7 @@
       <c r="G245" t="n">
         <v>1</v>
       </c>
-      <c r="H245" s="2" t="n">
+      <c r="H245" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I245" t="inlineStr">
@@ -12222,7 +12210,7 @@
         <v>0.3666666666666666</v>
       </c>
       <c r="E246" t="n">
-        <v>0.3057896596415205</v>
+        <v>0.3057896596415204</v>
       </c>
       <c r="F246" t="n">
         <v>2024</v>
@@ -12230,7 +12218,7 @@
       <c r="G246" t="n">
         <v>1</v>
       </c>
-      <c r="H246" s="2" t="n">
+      <c r="H246" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I246" t="inlineStr">
@@ -12270,7 +12258,7 @@
         <v>0.3317460317460317</v>
       </c>
       <c r="E247" t="n">
-        <v>0.332100762681156</v>
+        <v>0.3321007626811561</v>
       </c>
       <c r="F247" t="n">
         <v>2024</v>
@@ -12278,7 +12266,7 @@
       <c r="G247" t="n">
         <v>1</v>
       </c>
-      <c r="H247" s="2" t="n">
+      <c r="H247" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I247" t="inlineStr">
@@ -12326,7 +12314,7 @@
       <c r="G248" t="n">
         <v>1</v>
       </c>
-      <c r="H248" s="2" t="n">
+      <c r="H248" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I248" t="inlineStr">
@@ -12374,7 +12362,7 @@
       <c r="G249" t="n">
         <v>1</v>
       </c>
-      <c r="H249" s="2" t="n">
+      <c r="H249" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I249" t="inlineStr">
@@ -12422,7 +12410,7 @@
       <c r="G250" t="n">
         <v>1</v>
       </c>
-      <c r="H250" s="2" t="n">
+      <c r="H250" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I250" t="inlineStr">
@@ -12462,7 +12450,7 @@
         <v>0.1571428571428571</v>
       </c>
       <c r="E251" t="n">
-        <v>0.3204248455954963</v>
+        <v>0.3204248455954964</v>
       </c>
       <c r="F251" t="n">
         <v>2024</v>
@@ -12470,7 +12458,7 @@
       <c r="G251" t="n">
         <v>1</v>
       </c>
-      <c r="H251" s="2" t="n">
+      <c r="H251" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I251" t="inlineStr">
@@ -12518,7 +12506,7 @@
       <c r="G252" t="n">
         <v>2</v>
       </c>
-      <c r="H252" s="2" t="n">
+      <c r="H252" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I252" t="inlineStr">
@@ -12566,7 +12554,7 @@
       <c r="G253" t="n">
         <v>2</v>
       </c>
-      <c r="H253" s="2" t="n">
+      <c r="H253" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I253" t="inlineStr">
@@ -12606,7 +12594,7 @@
         <v>0.4095238095238095</v>
       </c>
       <c r="E254" t="n">
-        <v>0.273367245165357</v>
+        <v>0.2733672451653571</v>
       </c>
       <c r="F254" t="n">
         <v>2024</v>
@@ -12614,7 +12602,7 @@
       <c r="G254" t="n">
         <v>2</v>
       </c>
-      <c r="H254" s="2" t="n">
+      <c r="H254" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I254" t="inlineStr">
@@ -12662,7 +12650,7 @@
       <c r="G255" t="n">
         <v>2</v>
       </c>
-      <c r="H255" s="2" t="n">
+      <c r="H255" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I255" t="inlineStr">
@@ -12710,7 +12698,7 @@
       <c r="G256" t="n">
         <v>2</v>
       </c>
-      <c r="H256" s="2" t="n">
+      <c r="H256" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I256" t="inlineStr">
@@ -12758,7 +12746,7 @@
       <c r="G257" t="n">
         <v>2</v>
       </c>
-      <c r="H257" s="2" t="n">
+      <c r="H257" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I257" t="inlineStr">
@@ -12806,7 +12794,7 @@
       <c r="G258" t="n">
         <v>2</v>
       </c>
-      <c r="H258" s="2" t="n">
+      <c r="H258" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I258" t="inlineStr">
@@ -12854,7 +12842,7 @@
       <c r="G259" t="n">
         <v>2</v>
       </c>
-      <c r="H259" s="2" t="n">
+      <c r="H259" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I259" t="inlineStr">
@@ -12902,7 +12890,7 @@
       <c r="G260" t="n">
         <v>2</v>
       </c>
-      <c r="H260" s="2" t="n">
+      <c r="H260" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I260" t="inlineStr">
@@ -12950,7 +12938,7 @@
       <c r="G261" t="n">
         <v>2</v>
       </c>
-      <c r="H261" s="2" t="n">
+      <c r="H261" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I261" t="inlineStr">
@@ -12998,7 +12986,7 @@
       <c r="G262" t="n">
         <v>3</v>
       </c>
-      <c r="H262" s="2" t="n">
+      <c r="H262" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I262" t="inlineStr">
@@ -13046,7 +13034,7 @@
       <c r="G263" t="n">
         <v>3</v>
       </c>
-      <c r="H263" s="2" t="n">
+      <c r="H263" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I263" t="inlineStr">
@@ -13094,7 +13082,7 @@
       <c r="G264" t="n">
         <v>3</v>
       </c>
-      <c r="H264" s="2" t="n">
+      <c r="H264" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I264" t="inlineStr">
@@ -13142,7 +13130,7 @@
       <c r="G265" t="n">
         <v>3</v>
       </c>
-      <c r="H265" s="2" t="n">
+      <c r="H265" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I265" t="inlineStr">
@@ -13190,7 +13178,7 @@
       <c r="G266" t="n">
         <v>3</v>
       </c>
-      <c r="H266" s="2" t="n">
+      <c r="H266" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I266" t="inlineStr">
@@ -13238,7 +13226,7 @@
       <c r="G267" t="n">
         <v>3</v>
       </c>
-      <c r="H267" s="2" t="n">
+      <c r="H267" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I267" t="inlineStr">
@@ -13286,7 +13274,7 @@
       <c r="G268" t="n">
         <v>3</v>
       </c>
-      <c r="H268" s="2" t="n">
+      <c r="H268" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I268" t="inlineStr">
@@ -13334,7 +13322,7 @@
       <c r="G269" t="n">
         <v>3</v>
       </c>
-      <c r="H269" s="2" t="n">
+      <c r="H269" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I269" t="inlineStr">
@@ -13382,7 +13370,7 @@
       <c r="G270" t="n">
         <v>3</v>
       </c>
-      <c r="H270" s="2" t="n">
+      <c r="H270" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I270" t="inlineStr">
@@ -13430,7 +13418,7 @@
       <c r="G271" t="n">
         <v>3</v>
       </c>
-      <c r="H271" s="2" t="n">
+      <c r="H271" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I271" t="inlineStr">
@@ -13470,7 +13458,7 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="E272" t="n">
-        <v>0.2860546723538214</v>
+        <v>0.2860546723538215</v>
       </c>
       <c r="F272" t="n">
         <v>2024</v>
@@ -13478,7 +13466,7 @@
       <c r="G272" t="n">
         <v>4</v>
       </c>
-      <c r="H272" s="2" t="n">
+      <c r="H272" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I272" t="inlineStr">
@@ -13526,7 +13514,7 @@
       <c r="G273" t="n">
         <v>4</v>
       </c>
-      <c r="H273" s="2" t="n">
+      <c r="H273" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I273" t="inlineStr">
@@ -13574,7 +13562,7 @@
       <c r="G274" t="n">
         <v>4</v>
       </c>
-      <c r="H274" s="2" t="n">
+      <c r="H274" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I274" t="inlineStr">
@@ -13622,7 +13610,7 @@
       <c r="G275" t="n">
         <v>4</v>
       </c>
-      <c r="H275" s="2" t="n">
+      <c r="H275" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I275" t="inlineStr">
@@ -13662,7 +13650,7 @@
         <v>0.2587301587301588</v>
       </c>
       <c r="E276" t="n">
-        <v>0.1722117641352127</v>
+        <v>0.1722117641352128</v>
       </c>
       <c r="F276" t="n">
         <v>2024</v>
@@ -13670,7 +13658,7 @@
       <c r="G276" t="n">
         <v>4</v>
       </c>
-      <c r="H276" s="2" t="n">
+      <c r="H276" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I276" t="inlineStr">
@@ -13710,7 +13698,7 @@
         <v>0.2079365079365079</v>
       </c>
       <c r="E277" t="n">
-        <v>0.2214435929235694</v>
+        <v>0.2214435929235695</v>
       </c>
       <c r="F277" t="n">
         <v>2024</v>
@@ -13718,7 +13706,7 @@
       <c r="G277" t="n">
         <v>4</v>
       </c>
-      <c r="H277" s="2" t="n">
+      <c r="H277" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I277" t="inlineStr">
@@ -13766,7 +13754,7 @@
       <c r="G278" t="n">
         <v>4</v>
       </c>
-      <c r="H278" s="2" t="n">
+      <c r="H278" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I278" t="inlineStr">
@@ -13814,7 +13802,7 @@
       <c r="G279" t="n">
         <v>4</v>
       </c>
-      <c r="H279" s="2" t="n">
+      <c r="H279" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I279" t="inlineStr">
@@ -13862,7 +13850,7 @@
       <c r="G280" t="n">
         <v>4</v>
       </c>
-      <c r="H280" s="2" t="n">
+      <c r="H280" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I280" t="inlineStr">
@@ -13910,7 +13898,7 @@
       <c r="G281" t="n">
         <v>4</v>
       </c>
-      <c r="H281" s="2" t="n">
+      <c r="H281" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="I281" t="inlineStr">
